--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.14397853698888</v>
+        <v>5.873396512260692</v>
       </c>
       <c r="D2" t="n">
-        <v>5.073359277344526</v>
+        <v>0.8244208825684854</v>
       </c>
       <c r="E2" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F2" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.93969439261887</v>
+        <v>5.190200338800567</v>
       </c>
       <c r="D3" t="n">
-        <v>19.91225010680323</v>
+        <v>3.235740642355525</v>
       </c>
       <c r="E3" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F3" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.24807514624935</v>
+        <v>5.565312211265519</v>
       </c>
       <c r="D4" t="n">
-        <v>29.74184413656301</v>
+        <v>4.833049672191489</v>
       </c>
       <c r="E4" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F4" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.48666559416124</v>
+        <v>6.091583159051202</v>
       </c>
       <c r="D5" t="n">
-        <v>29.84093227875806</v>
+        <v>4.849151495298186</v>
       </c>
       <c r="E5" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F5" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.41250424955256</v>
+        <v>5.429531940552292</v>
       </c>
       <c r="D6" t="n">
-        <v>33.32623309092734</v>
+        <v>5.415512877275693</v>
       </c>
       <c r="E6" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F6" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.43282571177215</v>
+        <v>9.170334178162975</v>
       </c>
       <c r="D7" t="n">
-        <v>58.28897703828716</v>
+        <v>9.471958768721665</v>
       </c>
       <c r="E7" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F7" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.32713287165273</v>
+        <v>2.165659091643569</v>
       </c>
       <c r="D8" t="n">
-        <v>8.243143641981362</v>
+        <v>1.339510841821971</v>
       </c>
       <c r="E8" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F8" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.75498700306155</v>
+        <v>3.860185387997503</v>
       </c>
       <c r="D9" t="n">
-        <v>12.93520669108526</v>
+        <v>2.101971087301355</v>
       </c>
       <c r="E9" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F9" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>92.21054519566428</v>
+        <v>14.98421359429545</v>
       </c>
       <c r="D10" t="n">
-        <v>83.09882059006355</v>
+        <v>13.50355834588533</v>
       </c>
       <c r="E10" t="n">
-        <v>21.43163312864603</v>
+        <v>3.48264038340498</v>
       </c>
       <c r="F10" t="n">
-        <v>23.81973085341622</v>
+        <v>3.870706263680136</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
